--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.7354181698063</v>
+        <v>8.569505452593525</v>
       </c>
       <c r="D2" t="n">
-        <v>1.54660498432073</v>
+        <v>0.2513233099521186</v>
       </c>
       <c r="E2" t="n">
-        <v>20.62876329259064</v>
+        <v>3.35217403504598</v>
       </c>
       <c r="F2" t="n">
-        <v>36.88974832593492</v>
+        <v>5.994584102964424</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.00177424487921</v>
+        <v>7.312788314792873</v>
       </c>
       <c r="D3" t="n">
-        <v>44.92407570491542</v>
+        <v>7.300162302048757</v>
       </c>
       <c r="E3" t="n">
-        <v>20.62876329259064</v>
+        <v>3.35217403504598</v>
       </c>
       <c r="F3" t="n">
-        <v>36.88974832593492</v>
+        <v>5.994584102964424</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>92.11324328822015</v>
+        <v>14.96840203433577</v>
       </c>
       <c r="D4" t="n">
-        <v>91.88399049443271</v>
+        <v>14.93114845534532</v>
       </c>
       <c r="E4" t="n">
-        <v>20.62876329259064</v>
+        <v>3.35217403504598</v>
       </c>
       <c r="F4" t="n">
-        <v>36.88974832593492</v>
+        <v>5.994584102964424</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
